--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -19002,6 +19002,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="811">
+      <c r="A811" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B811" t="n">
+        <v>0</v>
+      </c>
+      <c r="C811" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="D811" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="E811" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="F811" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="G811" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B812" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C812" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="D812" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="E812" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="F812" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G812" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -19048,6 +19048,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="813">
+      <c r="A813" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B813" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C813" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="D813" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="E813" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="F813" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="G813" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -19071,6 +19071,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="814">
+      <c r="A814" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B814" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C814" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="D814" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="E814" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="F814" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="G814" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -19094,6 +19094,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="815">
+      <c r="A815" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B815" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C815" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="D815" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="E815" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="F815" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="G815" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -18935,22 +18935,22 @@
     </row>
     <row r="808">
       <c r="A808" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B808" t="n">
-        <v>11000</v>
+        <v>14000</v>
       </c>
       <c r="C808" t="n">
-        <v>1.17999994754791</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="D808" t="n">
-        <v>1.17999994754791</v>
+        <v>1.19000005722046</v>
       </c>
       <c r="E808" t="n">
-        <v>1.17999994754791</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="F808" t="n">
-        <v>1.17999994754791</v>
+        <v>1.19000005722046</v>
       </c>
       <c r="G808" t="s">
         <v>7</v>
@@ -18958,10 +18958,10 @@
     </row>
     <row r="809">
       <c r="A809" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B809" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="C809" t="n">
         <v>1.17999994754791</v>
@@ -18981,13 +18981,13 @@
     </row>
     <row r="810">
       <c r="A810" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B810" t="n">
-        <v>24000</v>
+        <v>2000</v>
       </c>
       <c r="C810" t="n">
-        <v>1.21000003814697</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="D810" t="n">
         <v>1.17999994754791</v>
@@ -18996,7 +18996,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="F810" t="n">
-        <v>1.20000004768372</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="G810" t="s">
         <v>7</v>
@@ -19004,19 +19004,19 @@
     </row>
     <row r="811">
       <c r="A811" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B811" t="n">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="C811" t="n">
-        <v>1.20000004768372</v>
+        <v>1.21000003814697</v>
       </c>
       <c r="D811" t="n">
-        <v>1.20000004768372</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="E811" t="n">
-        <v>1.20000004768372</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="F811" t="n">
         <v>1.20000004768372</v>
@@ -19027,22 +19027,22 @@
     </row>
     <row r="812">
       <c r="A812" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B812" t="n">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="C812" t="n">
-        <v>1.21000003814697</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="D812" t="n">
-        <v>1.17999994754791</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="E812" t="n">
-        <v>1.21000003814697</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="F812" t="n">
-        <v>1.21000003814697</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="G812" t="s">
         <v>7</v>
@@ -19050,22 +19050,22 @@
     </row>
     <row r="813">
       <c r="A813" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B813" t="n">
-        <v>16000</v>
+        <v>14000</v>
       </c>
       <c r="C813" t="n">
-        <v>1.24000000953674</v>
+        <v>1.21000003814697</v>
       </c>
       <c r="D813" t="n">
-        <v>1.21000003814697</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="E813" t="n">
         <v>1.21000003814697</v>
       </c>
       <c r="F813" t="n">
-        <v>1.23000001907349</v>
+        <v>1.21000003814697</v>
       </c>
       <c r="G813" t="s">
         <v>7</v>
@@ -19073,22 +19073,22 @@
     </row>
     <row r="814">
       <c r="A814" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B814" t="n">
-        <v>22000</v>
+        <v>16000</v>
       </c>
       <c r="C814" t="n">
         <v>1.24000000953674</v>
       </c>
       <c r="D814" t="n">
-        <v>1.22000002861023</v>
+        <v>1.21000003814697</v>
       </c>
       <c r="E814" t="n">
-        <v>1.22000002861023</v>
+        <v>1.21000003814697</v>
       </c>
       <c r="F814" t="n">
-        <v>1.24000000953674</v>
+        <v>1.23000001907349</v>
       </c>
       <c r="G814" t="s">
         <v>7</v>
@@ -19096,24 +19096,47 @@
     </row>
     <row r="815">
       <c r="A815" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B815" t="n">
-        <v>10000</v>
+        <v>22000</v>
       </c>
       <c r="C815" t="n">
         <v>1.24000000953674</v>
       </c>
       <c r="D815" t="n">
-        <v>1.24000000953674</v>
+        <v>1.22000002861023</v>
       </c>
       <c r="E815" t="n">
-        <v>1.24000000953674</v>
+        <v>1.22000002861023</v>
       </c>
       <c r="F815" t="n">
         <v>1.24000000953674</v>
       </c>
       <c r="G815" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B816" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C816" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="D816" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="E816" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="F816" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="G816" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -21643,6 +21643,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="819">
+      <c r="A819" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B819" t="n">
+        <v>24000</v>
+      </c>
+      <c r="C819" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="D819" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="E819" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="F819" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="G819" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="H819" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -21669,6 +21669,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="820">
+      <c r="A820" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B820" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C820" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="D820" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="E820" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="F820" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="G820" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="H820" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -21695,6 +21695,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="821">
+      <c r="A821" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B821" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C821" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="D821" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="E821" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="F821" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G821" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="H821" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -21721,6 +21721,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="822">
+      <c r="A822" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B822" t="n">
+        <v>29000</v>
+      </c>
+      <c r="C822" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="D822" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="E822" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="F822" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="G822" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="H822" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -21799,6 +21799,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="825">
+      <c r="A825" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B825" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C825" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="D825" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="E825" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="F825" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="G825" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="H825" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -19409,7 +19409,9 @@
       <c r="E828" t="n">
         <v>1.20000004768372</v>
       </c>
-      <c r="F828"/>
+      <c r="F828" t="n">
+        <v>1.17999994754791</v>
+      </c>
       <c r="G828" t="s">
         <v>7</v>
       </c>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -19416,6 +19416,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="829">
+      <c r="A829" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B829" t="n">
+        <v>0</v>
+      </c>
+      <c r="C829" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="D829" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="E829" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="F829" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="G829" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -19439,6 +19439,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="830">
+      <c r="A830" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B830" t="n">
+        <v>0</v>
+      </c>
+      <c r="C830" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="D830" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="E830" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="F830" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="G830" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B831" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C831" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="D831" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="E831" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="F831"/>
+      <c r="G831" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -19478,7 +19478,9 @@
       <c r="E831" t="n">
         <v>1.19000005722046</v>
       </c>
-      <c r="F831"/>
+      <c r="F831" t="n">
+        <v>1.17999994754791</v>
+      </c>
       <c r="G831" t="s">
         <v>7</v>
       </c>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -19508,6 +19508,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="833">
+      <c r="A833" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B833" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C833" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D833" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E833" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F833" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="G833" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -19531,6 +19531,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="834">
+      <c r="A834" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B834" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C834" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="D834" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E834" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F834" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="G834" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -24651,6 +24651,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="838">
+      <c r="A838" t="s">
+        <v>9</v>
+      </c>
+      <c r="B838" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C838" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D838" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E838" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F838" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="G838" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="H838" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I838" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -24680,6 +24680,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="839">
+      <c r="A839" t="s">
+        <v>9</v>
+      </c>
+      <c r="B839" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C839" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D839" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E839" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F839" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="G839" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="H839" t="n">
+        <v>0</v>
+      </c>
+      <c r="I839" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="s">
+        <v>9</v>
+      </c>
+      <c r="B840" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C840" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D840" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E840" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F840" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G840" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="H840" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I840" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -24732,7 +24732,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="H840" t="n">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="I840" t="s">
         <v>9</v>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -24738,6 +24738,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="841">
+      <c r="A841" t="s">
+        <v>9</v>
+      </c>
+      <c r="B841" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C841" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D841" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E841" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F841" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G841" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="H841" t="n">
+        <v>0</v>
+      </c>
+      <c r="I841" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="s">
+        <v>9</v>
+      </c>
+      <c r="B842" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C842" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D842" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E842" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F842" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G842" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="H842" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I842" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -24796,6 +24796,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="843">
+      <c r="A843" t="s">
+        <v>9</v>
+      </c>
+      <c r="B843" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C843" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D843" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E843" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F843" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G843" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="H843" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I843" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -24825,6 +24825,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="844">
+      <c r="A844" t="s">
+        <v>9</v>
+      </c>
+      <c r="B844" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C844" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="D844" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="E844" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="F844" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="G844" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="H844" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I844" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -24854,6 +24854,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="845">
+      <c r="A845" t="s">
+        <v>9</v>
+      </c>
+      <c r="B845" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C845" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="D845" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="E845" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="F845" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="G845" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="H845" t="n">
+        <v>0</v>
+      </c>
+      <c r="I845" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="s">
+        <v>9</v>
+      </c>
+      <c r="B846" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C846" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="D846" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="E846" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="F846" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="G846" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="H846" t="n">
+        <v>21000</v>
+      </c>
+      <c r="I846" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFLTC.MI.xlsx
+++ b/data/RFLTC.MI.xlsx
@@ -24912,6 +24912,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="847">
+      <c r="A847" t="s">
+        <v>9</v>
+      </c>
+      <c r="B847" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C847" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="D847" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="E847" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="F847" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="G847" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="H847" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I847" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
